--- a/プロジェクト型演習_成果物_TasBo_削除.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_削除.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER110\Desktop\プロジェクト演習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\削除\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B757772-7D6B-405D-8A6D-7418BA76B5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D749623-3011-459F-9A23-F7248BA47ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="11" r:id="rId1"/>
-    <sheet name="ユースケース記述" sheetId="12" r:id="rId2"/>
+    <sheet name="ユースケース記述" sheetId="18" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書 (削除確認本人以外)" sheetId="17" r:id="rId5"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="115">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -548,6 +548,102 @@
       <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>栗原</t>
+    <rPh sb="0" eb="2">
+      <t>クリハラ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク削除</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>対象タスクが削除されている。/タスク一覧から削除対象が削除されている。</t>
+    <rPh sb="27" eb="29">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザが登録済みのタスクを削除する。</t>
+    <rPh sb="4" eb="5">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザはタスク一覧画面で削除対象のタスクを選択する。
+システムは削除確認画面を表示する。
+ユーザは削除内容を確認する。
+ユーザは「削除確定」ボタンを押下する。
+システムは対象タスクの削除処理を実行する。
+システムは削除完了メッセージを表示する。
+システムはタスク一覧画面へ遷移する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザがシステムにログインしていること
+データベースに削除対象のタスクが存在していること
+タスク一覧画面が表示されていること
+削除対象のタスクがログイン中ユーザの登録したタスクであること</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1.削除をキャンセルした場合
+a. ユーザが「キャンセル」を選択する。
+b. システムは削除処理を行わない。
+c. システムは前画面（一覧または詳細画面）へ戻る。
+A2.対象タスクが既に削除されている場合
+a. システムは削除処理を開始する。
+b. 対象タスクが存在しないことを検出する。
+c. システムはエラーメッセージを表示する。
+d. システムはタスク一覧画面へ遷移する。
+A3. 他ユーザのタスクを削除しようとした場合
+a.ユーザが削除対象のタスクを選択する。
+b.システムは対象タスクの所有者を確認する。
+c.システムは対象タスクがログイン中ユーザのタスクではないことを検出する。
+d.システムは「タスクの削除は本人しか行うことはできません」などのエラーメッセージを表示する。
+e.システムはタスク一覧画面へ遷移する。</t>
+    <rPh sb="311" eb="313">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="314" eb="316">
+      <t>ホンニン</t>
+    </rPh>
+    <rPh sb="318" eb="319">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザは自身が登録したタスクのみ削除できる。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1. システムエラーが発生した場合
+a. システムエラーが発生する。
+b. システムは「エラーが発生しました」等エラーメッセージを表示する。
+c. システムは処理を終了する。</t>
+    <rPh sb="49" eb="51">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ナド</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -1865,6 +1961,213 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1880,6 +2183,39 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1894,246 +2230,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -3500,85 +3596,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="111" t="s">
+      <c r="C2" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
       <c r="P2" s="66"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="100"/>
+      <c r="O3" s="100"/>
       <c r="P3" s="66"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="100"/>
       <c r="P4" s="66"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="110"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="100"/>
       <c r="P5" s="66"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="110"/>
-      <c r="M6" s="110"/>
-      <c r="N6" s="110"/>
-      <c r="O6" s="110"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="100"/>
+      <c r="N6" s="100"/>
+      <c r="O6" s="100"/>
       <c r="P6" s="66"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
@@ -3598,46 +3694,46 @@
       <c r="P7" s="66"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="113" t="s">
+      <c r="E8" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="110"/>
-      <c r="M8" s="110"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="100"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="100"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="100"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="106" t="s">
+      <c r="G13" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="108"/>
-      <c r="I13" s="114">
-        <v>46175</v>
-      </c>
-      <c r="J13" s="107"/>
-      <c r="K13" s="108"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="116">
+        <v>46191</v>
+      </c>
+      <c r="J13" s="71"/>
+      <c r="K13" s="74"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="106"/>
-      <c r="H14" s="108"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="107"/>
-      <c r="K14" s="108"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="74"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="106"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="107"/>
-      <c r="K15" s="108"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="74"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="65"/>
@@ -3646,13 +3742,13 @@
       <c r="J16" s="65"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="109" t="s">
+      <c r="G17" s="112" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -8184,7 +8280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B01C408-717E-4B3D-9584-3B31171939C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C4D44D-FFA7-4AA2-948D-F8FC774EF950}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -8195,19 +8291,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="142" t="s">
+      <c r="B1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="141"/>
-      <c r="F1" s="142" t="s">
+      <c r="E1" s="93"/>
+      <c r="F1" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="141"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="69" t="s">
         <v>5</v>
       </c>
@@ -8219,172 +8315,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="134"/>
-      <c r="B2" s="110"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="143" t="s">
+      <c r="A2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="144"/>
-      <c r="F2" s="143" t="s">
+      <c r="E2" s="107"/>
+      <c r="F2" s="106" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="144"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="128"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="110">
+        <v>46191</v>
+      </c>
+      <c r="I2" s="85" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="88"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="134"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="129"/>
+      <c r="A3" s="99"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="89"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="136"/>
-      <c r="B4" s="137"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="130"/>
+      <c r="A4" s="102"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="90"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="140"/>
-      <c r="C5" s="141"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="152"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="94" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="95"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="115" t="s">
+      <c r="A6" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="107"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="107"/>
-      <c r="I6" s="107"/>
-      <c r="J6" s="124"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="115" t="s">
+      <c r="A7" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="107"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="124"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="115" t="s">
+      <c r="B7" s="71"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="75" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="72"/>
+    </row>
+    <row r="8" spans="1:10" ht="73.5" customHeight="1">
+      <c r="A8" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="107"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="124"/>
-    </row>
-    <row r="9" spans="1:10" ht="106.5" customHeight="1">
-      <c r="A9" s="116" t="s">
+      <c r="B8" s="71"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="70" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="72"/>
+    </row>
+    <row r="9" spans="1:10" ht="120.75" customHeight="1">
+      <c r="A9" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="119" t="s">
+      <c r="B9" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="108"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="124"/>
-    </row>
-    <row r="10" spans="1:10" ht="126.75" customHeight="1">
-      <c r="A10" s="117"/>
-      <c r="B10" s="119" t="s">
+      <c r="C9" s="74"/>
+      <c r="D9" s="70" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+    </row>
+    <row r="10" spans="1:10" ht="249.75" customHeight="1">
+      <c r="A10" s="82"/>
+      <c r="B10" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="108"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="107"/>
-      <c r="J10" s="124"/>
-    </row>
-    <row r="11" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119" t="s">
+      <c r="C10" s="74"/>
+      <c r="D10" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="83"/>
+      <c r="B11" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="108"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="107"/>
-      <c r="F11" s="107"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="107"/>
-      <c r="I11" s="107"/>
-      <c r="J11" s="124"/>
-    </row>
-    <row r="12" spans="1:10" ht="48.75" customHeight="1">
-      <c r="A12" s="115" t="s">
+      <c r="C11" s="74"/>
+      <c r="D11" s="70" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="107"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="107"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="107"/>
-      <c r="I12" s="107"/>
-      <c r="J12" s="124"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="75" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="125" t="s">
+      <c r="A13" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="121"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="122"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="79" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="80"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9375,33 +9493,33 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
     <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="A13:C13"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -9420,19 +9538,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="88"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="133"/>
+      <c r="F1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="88"/>
+      <c r="G1" s="133"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -9444,40 +9562,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="84"/>
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="120"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="121"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="155"/>
-      <c r="B4" s="156"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="157"/>
-      <c r="H4" s="153"/>
-      <c r="I4" s="153"/>
-      <c r="J4" s="154"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -10833,19 +10951,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="123" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="88"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="133"/>
+      <c r="F1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="88"/>
+      <c r="G1" s="133"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -10857,48 +10975,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="135"/>
+      <c r="F2" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="159">
+      <c r="G2" s="135"/>
+      <c r="H2" s="138">
         <v>46189</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="120"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="121"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="155"/>
-      <c r="B4" s="156"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="157"/>
-      <c r="H4" s="153"/>
-      <c r="I4" s="153"/>
-      <c r="J4" s="154"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -12345,19 +12463,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="88"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="133"/>
+      <c r="F1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="88"/>
+      <c r="G1" s="133"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -12369,190 +12487,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="135"/>
+      <c r="F2" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="105">
+      <c r="G2" s="135"/>
+      <c r="H2" s="153">
         <v>46189</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="120"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="121"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="89" t="s">
+      <c r="B5" s="145"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="146" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="90"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="147"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="74"/>
+      <c r="B6" s="140"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="143"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="94"/>
-      <c r="B8" s="95"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="96"/>
+      <c r="A8" s="126"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="152"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="94"/>
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="96"/>
+      <c r="A9" s="126"/>
+      <c r="B9" s="127"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="127"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="152"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="94"/>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="96"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="152"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="94"/>
-      <c r="B11" s="95"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="96"/>
+      <c r="A11" s="126"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="152"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="96"/>
+      <c r="A12" s="126"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="152"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="96"/>
+      <c r="A13" s="126"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="152"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="74"/>
+      <c r="B14" s="140"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="143"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="73" t="s">
+      <c r="B15" s="140"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="142" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="141"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
@@ -12561,11 +12679,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="80" t="s">
+      <c r="A16" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="141"/>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
@@ -12578,18 +12696,18 @@
       <c r="G16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="81" t="s">
+      <c r="H16" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="74"/>
+      <c r="I16" s="140"/>
+      <c r="J16" s="143"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="70">
+      <c r="A17" s="139">
         <v>1</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="B17" s="140"/>
+      <c r="C17" s="141"/>
       <c r="D17" s="14" t="s">
         <v>101</v>
       </c>
@@ -12600,81 +12718,81 @@
       <c r="G17" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="73"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="74"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="140"/>
+      <c r="J17" s="143"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="70"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
+      <c r="A18" s="139"/>
+      <c r="B18" s="140"/>
+      <c r="C18" s="141"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="74"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="143"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="70"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
+      <c r="A19" s="139"/>
+      <c r="B19" s="140"/>
+      <c r="C19" s="141"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="74"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="140"/>
+      <c r="J19" s="143"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="70"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
+      <c r="A20" s="139"/>
+      <c r="B20" s="140"/>
+      <c r="C20" s="141"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="74"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="140"/>
+      <c r="J20" s="143"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="70"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
+      <c r="A21" s="139"/>
+      <c r="B21" s="140"/>
+      <c r="C21" s="141"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="74"/>
+      <c r="H21" s="142"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="143"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="70"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="72"/>
+      <c r="A22" s="139"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="141"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="74"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="143"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="75"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="77"/>
+      <c r="A23" s="155"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="157"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="79"/>
+      <c r="H23" s="158"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="159"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13655,23 +13773,21 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -13686,6 +13802,8 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13708,19 +13826,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="88"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="133"/>
+      <c r="F1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="88"/>
+      <c r="G1" s="133"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -13732,190 +13850,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="135"/>
+      <c r="F2" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="105">
+      <c r="G2" s="135"/>
+      <c r="H2" s="153">
         <v>46189</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="120"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="121"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="89" t="s">
+      <c r="B5" s="145"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="146" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="90"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="147"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="74"/>
+      <c r="B6" s="140"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="143"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="94"/>
-      <c r="B8" s="95"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="96"/>
+      <c r="A8" s="126"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="152"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="94"/>
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="96"/>
+      <c r="A9" s="126"/>
+      <c r="B9" s="127"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="127"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="152"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="94"/>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="96"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="152"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="94"/>
-      <c r="B11" s="95"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="96"/>
+      <c r="A11" s="126"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="152"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="96"/>
+      <c r="A12" s="126"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="152"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="96"/>
+      <c r="A13" s="126"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="152"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="74"/>
+      <c r="B14" s="140"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="143"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="73" t="s">
+      <c r="B15" s="140"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="142" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="141"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
@@ -13924,11 +14042,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="80" t="s">
+      <c r="A16" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="141"/>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
@@ -13941,18 +14059,18 @@
       <c r="G16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="81" t="s">
+      <c r="H16" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="74"/>
+      <c r="I16" s="140"/>
+      <c r="J16" s="143"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="70">
+      <c r="A17" s="139">
         <v>1</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="B17" s="140"/>
+      <c r="C17" s="141"/>
       <c r="D17" s="14" t="s">
         <v>98</v>
       </c>
@@ -13963,49 +14081,49 @@
       <c r="G17" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="H17" s="73"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="74"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="140"/>
+      <c r="J17" s="143"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="70"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
+      <c r="A18" s="139"/>
+      <c r="B18" s="140"/>
+      <c r="C18" s="141"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="74"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="143"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="80" t="s">
+      <c r="A19" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="74"/>
+      <c r="B19" s="140"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="140"/>
+      <c r="F19" s="140"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="140"/>
+      <c r="I19" s="140"/>
+      <c r="J19" s="143"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="73" t="s">
+      <c r="B20" s="140"/>
+      <c r="C20" s="141"/>
+      <c r="D20" s="142" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="72"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="141"/>
       <c r="I20" s="12" t="s">
         <v>25</v>
       </c>
@@ -14014,11 +14132,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
+      <c r="B21" s="140"/>
+      <c r="C21" s="141"/>
       <c r="D21" s="12" t="s">
         <v>27</v>
       </c>
@@ -14031,18 +14149,18 @@
       <c r="G21" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="81" t="s">
+      <c r="H21" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="71"/>
-      <c r="J21" s="74"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="143"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A22" s="75">
+      <c r="A22" s="155">
         <v>2</v>
       </c>
-      <c r="B22" s="76"/>
-      <c r="C22" s="77"/>
+      <c r="B22" s="156"/>
+      <c r="C22" s="157"/>
       <c r="D22" s="16" t="s">
         <v>100</v>
       </c>
@@ -14053,9 +14171,9 @@
       <c r="G22" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="78"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="79"/>
+      <c r="H22" s="158"/>
+      <c r="I22" s="156"/>
+      <c r="J22" s="159"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -15036,13 +15154,8 @@
     <row r="999" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -15050,13 +15163,18 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
@@ -15086,19 +15204,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="88"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="133"/>
+      <c r="F1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="88"/>
+      <c r="G1" s="133"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -15110,190 +15228,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="135"/>
+      <c r="F2" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="105">
+      <c r="G2" s="135"/>
+      <c r="H2" s="153">
         <v>46189</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="120"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="121"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="89" t="s">
+      <c r="B5" s="145"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="146" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="90"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="147"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="74"/>
+      <c r="B6" s="140"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="143"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="94"/>
-      <c r="B8" s="95"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="96"/>
+      <c r="A8" s="126"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="152"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="94"/>
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="96"/>
+      <c r="A9" s="126"/>
+      <c r="B9" s="127"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="127"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="152"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="94"/>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="96"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="152"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="94"/>
-      <c r="B11" s="95"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="96"/>
+      <c r="A11" s="126"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="152"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="96"/>
+      <c r="A12" s="126"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="152"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="96"/>
+      <c r="A13" s="126"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="152"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="74"/>
+      <c r="B14" s="140"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="143"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="73" t="s">
+      <c r="B15" s="140"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="142" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="141"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
@@ -15302,11 +15420,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="80" t="s">
+      <c r="A16" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="141"/>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
@@ -15319,18 +15437,18 @@
       <c r="G16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="81" t="s">
+      <c r="H16" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="74"/>
+      <c r="I16" s="140"/>
+      <c r="J16" s="143"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="70">
+      <c r="A17" s="139">
         <v>1</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="B17" s="140"/>
+      <c r="C17" s="141"/>
       <c r="D17" s="14" t="s">
         <v>101</v>
       </c>
@@ -15341,81 +15459,81 @@
       <c r="G17" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="73"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="74"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="140"/>
+      <c r="J17" s="143"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="70"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
+      <c r="A18" s="139"/>
+      <c r="B18" s="140"/>
+      <c r="C18" s="141"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="74"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="143"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="70"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
+      <c r="A19" s="139"/>
+      <c r="B19" s="140"/>
+      <c r="C19" s="141"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="74"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="140"/>
+      <c r="J19" s="143"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="70"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
+      <c r="A20" s="139"/>
+      <c r="B20" s="140"/>
+      <c r="C20" s="141"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="74"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="140"/>
+      <c r="J20" s="143"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="70"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
+      <c r="A21" s="139"/>
+      <c r="B21" s="140"/>
+      <c r="C21" s="141"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="74"/>
+      <c r="H21" s="142"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="143"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="70"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="72"/>
+      <c r="A22" s="139"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="141"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="74"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="143"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="75"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="77"/>
+      <c r="A23" s="155"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="157"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="79"/>
+      <c r="H23" s="158"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="159"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -16396,13 +16514,8 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -16410,23 +16523,28 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -16449,19 +16567,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="88"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="133"/>
+      <c r="F1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="88"/>
+      <c r="G1" s="133"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -16473,190 +16591,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="135"/>
+      <c r="F2" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="105">
+      <c r="G2" s="135"/>
+      <c r="H2" s="153">
         <v>46189</v>
       </c>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="120"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="121"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="89" t="s">
+      <c r="B5" s="145"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="146" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="90"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="147"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="74"/>
+      <c r="B6" s="140"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="143"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="151"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="94"/>
-      <c r="B8" s="95"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="96"/>
+      <c r="A8" s="126"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="152"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="94"/>
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="96"/>
+      <c r="A9" s="126"/>
+      <c r="B9" s="127"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="127"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="152"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="94"/>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="96"/>
+      <c r="A10" s="126"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="152"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="94"/>
-      <c r="B11" s="95"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="96"/>
+      <c r="A11" s="126"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="152"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="96"/>
+      <c r="A12" s="126"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="152"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="96"/>
+      <c r="A13" s="126"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="152"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="74"/>
+      <c r="B14" s="140"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="143"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="73" t="s">
+      <c r="B15" s="140"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="142" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="141"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
@@ -16665,11 +16783,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="80" t="s">
+      <c r="A16" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="141"/>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
@@ -16682,18 +16800,18 @@
       <c r="G16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="81" t="s">
+      <c r="H16" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="74"/>
+      <c r="I16" s="140"/>
+      <c r="J16" s="143"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="70">
+      <c r="A17" s="139">
         <v>1</v>
       </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="B17" s="140"/>
+      <c r="C17" s="141"/>
       <c r="D17" s="14" t="s">
         <v>101</v>
       </c>
@@ -16704,81 +16822,81 @@
       <c r="G17" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="73"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="74"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="140"/>
+      <c r="J17" s="143"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="70"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
+      <c r="A18" s="139"/>
+      <c r="B18" s="140"/>
+      <c r="C18" s="141"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="74"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="143"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="70"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
+      <c r="A19" s="139"/>
+      <c r="B19" s="140"/>
+      <c r="C19" s="141"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="74"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="140"/>
+      <c r="J19" s="143"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="70"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
+      <c r="A20" s="139"/>
+      <c r="B20" s="140"/>
+      <c r="C20" s="141"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="74"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="140"/>
+      <c r="J20" s="143"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="70"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="72"/>
+      <c r="A21" s="139"/>
+      <c r="B21" s="140"/>
+      <c r="C21" s="141"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="74"/>
+      <c r="H21" s="142"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="143"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="70"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="72"/>
+      <c r="A22" s="139"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="141"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="74"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="143"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="75"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="77"/>
+      <c r="A23" s="155"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="157"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="79"/>
+      <c r="H23" s="158"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="159"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -17812,179 +17930,179 @@
       <c r="A1" s="171" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="101" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="101" t="s">
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="101" t="s">
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="132" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="101" t="s">
+      <c r="P1" s="133"/>
+      <c r="Q1" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="88"/>
-      <c r="S1" s="101" t="s">
+      <c r="R1" s="133"/>
+      <c r="S1" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="90"/>
+      <c r="T1" s="147"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="102" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="102" t="s">
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="103"/>
+      <c r="L2" s="150"/>
+      <c r="M2" s="150"/>
+      <c r="N2" s="135"/>
       <c r="O2" s="169"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="102" t="s">
+      <c r="P2" s="135"/>
+      <c r="Q2" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="103"/>
-      <c r="S2" s="102"/>
-      <c r="T2" s="93"/>
+      <c r="R2" s="135"/>
+      <c r="S2" s="134"/>
+      <c r="T2" s="151"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
-      <c r="N3" s="100"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="104"/>
-      <c r="R3" s="100"/>
-      <c r="S3" s="104"/>
-      <c r="T3" s="96"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="136"/>
+      <c r="T3" s="152"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="155"/>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="158"/>
-      <c r="H4" s="156"/>
-      <c r="I4" s="156"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="158"/>
-      <c r="L4" s="156"/>
-      <c r="M4" s="156"/>
-      <c r="N4" s="157"/>
-      <c r="O4" s="158"/>
-      <c r="P4" s="157"/>
-      <c r="Q4" s="158"/>
-      <c r="R4" s="157"/>
-      <c r="S4" s="158"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="131"/>
+      <c r="O4" s="137"/>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="131"/>
+      <c r="S4" s="137"/>
       <c r="T4" s="170"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="144" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="88"/>
+      <c r="B5" s="145"/>
+      <c r="C5" s="145"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="133"/>
       <c r="G5" s="166"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="87"/>
-      <c r="N5" s="87"/>
-      <c r="O5" s="87"/>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="87"/>
-      <c r="S5" s="87"/>
-      <c r="T5" s="90"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="145"/>
+      <c r="K5" s="145"/>
+      <c r="L5" s="145"/>
+      <c r="M5" s="145"/>
+      <c r="N5" s="145"/>
+      <c r="O5" s="145"/>
+      <c r="P5" s="145"/>
+      <c r="Q5" s="145"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="145"/>
+      <c r="T5" s="147"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="74"/>
+      <c r="B6" s="140"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="141"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="140"/>
+      <c r="N6" s="140"/>
+      <c r="O6" s="140"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="140"/>
+      <c r="R6" s="140"/>
+      <c r="S6" s="140"/>
+      <c r="T6" s="143"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="148" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="71"/>
-      <c r="T7" s="74"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="141"/>
+      <c r="G7" s="142"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="140"/>
+      <c r="L7" s="140"/>
+      <c r="M7" s="140"/>
+      <c r="N7" s="140"/>
+      <c r="O7" s="140"/>
+      <c r="P7" s="140"/>
+      <c r="Q7" s="140"/>
+      <c r="R7" s="140"/>
+      <c r="S7" s="140"/>
+      <c r="T7" s="143"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -18183,37 +18301,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="148" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="72"/>
+      <c r="B15" s="141"/>
       <c r="C15" s="168" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="72"/>
-      <c r="E15" s="81" t="s">
+      <c r="D15" s="141"/>
+      <c r="E15" s="154" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="72"/>
-      <c r="G15" s="81" t="s">
+      <c r="F15" s="141"/>
+      <c r="G15" s="154" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="71"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="81" t="s">
+      <c r="H15" s="140"/>
+      <c r="I15" s="141"/>
+      <c r="J15" s="154" t="s">
         <v>44</v>
       </c>
-      <c r="K15" s="72"/>
-      <c r="L15" s="81" t="s">
+      <c r="K15" s="141"/>
+      <c r="L15" s="154" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="71"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="81" t="s">
+      <c r="M15" s="140"/>
+      <c r="N15" s="141"/>
+      <c r="O15" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="72"/>
+      <c r="P15" s="140"/>
+      <c r="Q15" s="141"/>
       <c r="R15" s="12" t="s">
         <v>47</v>
       </c>
@@ -18228,22 +18346,22 @@
       <c r="A16" s="160">
         <v>1</v>
       </c>
-      <c r="B16" s="72"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="161"/>
-      <c r="D16" s="72"/>
+      <c r="D16" s="141"/>
       <c r="E16" s="161"/>
-      <c r="F16" s="72"/>
+      <c r="F16" s="141"/>
       <c r="G16" s="167"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="72"/>
+      <c r="H16" s="140"/>
+      <c r="I16" s="141"/>
       <c r="J16" s="167"/>
-      <c r="K16" s="72"/>
+      <c r="K16" s="141"/>
       <c r="L16" s="164"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="72"/>
+      <c r="M16" s="140"/>
+      <c r="N16" s="141"/>
       <c r="O16" s="164"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="72"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="141"/>
       <c r="R16" s="30"/>
       <c r="S16" s="30"/>
       <c r="T16" s="31"/>
@@ -18258,22 +18376,22 @@
       <c r="A17" s="160">
         <v>2</v>
       </c>
-      <c r="B17" s="72"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="161"/>
-      <c r="D17" s="72"/>
+      <c r="D17" s="141"/>
       <c r="E17" s="161"/>
-      <c r="F17" s="72"/>
+      <c r="F17" s="141"/>
       <c r="G17" s="167"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="72"/>
+      <c r="H17" s="140"/>
+      <c r="I17" s="141"/>
       <c r="J17" s="167"/>
-      <c r="K17" s="72"/>
+      <c r="K17" s="141"/>
       <c r="L17" s="164"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="72"/>
+      <c r="M17" s="140"/>
+      <c r="N17" s="141"/>
       <c r="O17" s="164"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="72"/>
+      <c r="P17" s="140"/>
+      <c r="Q17" s="141"/>
       <c r="R17" s="30"/>
       <c r="S17" s="30"/>
       <c r="T17" s="31"/>
@@ -18286,22 +18404,22 @@
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
       <c r="A18" s="160"/>
-      <c r="B18" s="72"/>
+      <c r="B18" s="141"/>
       <c r="C18" s="161"/>
-      <c r="D18" s="72"/>
+      <c r="D18" s="141"/>
       <c r="E18" s="161"/>
-      <c r="F18" s="72"/>
+      <c r="F18" s="141"/>
       <c r="G18" s="167"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="72"/>
+      <c r="H18" s="140"/>
+      <c r="I18" s="141"/>
       <c r="J18" s="167"/>
-      <c r="K18" s="72"/>
+      <c r="K18" s="141"/>
       <c r="L18" s="164"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="72"/>
+      <c r="M18" s="140"/>
+      <c r="N18" s="141"/>
       <c r="O18" s="164"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="72"/>
+      <c r="P18" s="140"/>
+      <c r="Q18" s="141"/>
       <c r="R18" s="30"/>
       <c r="S18" s="30"/>
       <c r="T18" s="31"/>
@@ -18314,22 +18432,22 @@
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
       <c r="A19" s="160"/>
-      <c r="B19" s="72"/>
+      <c r="B19" s="141"/>
       <c r="C19" s="161"/>
-      <c r="D19" s="72"/>
+      <c r="D19" s="141"/>
       <c r="E19" s="161"/>
-      <c r="F19" s="72"/>
+      <c r="F19" s="141"/>
       <c r="G19" s="167"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="72"/>
+      <c r="H19" s="140"/>
+      <c r="I19" s="141"/>
       <c r="J19" s="167"/>
-      <c r="K19" s="72"/>
+      <c r="K19" s="141"/>
       <c r="L19" s="164"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="72"/>
+      <c r="M19" s="140"/>
+      <c r="N19" s="141"/>
       <c r="O19" s="164"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="72"/>
+      <c r="P19" s="140"/>
+      <c r="Q19" s="141"/>
       <c r="R19" s="30"/>
       <c r="S19" s="30"/>
       <c r="T19" s="31"/>
@@ -18342,22 +18460,22 @@
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
       <c r="A20" s="160"/>
-      <c r="B20" s="72"/>
+      <c r="B20" s="141"/>
       <c r="C20" s="161"/>
-      <c r="D20" s="72"/>
+      <c r="D20" s="141"/>
       <c r="E20" s="161"/>
-      <c r="F20" s="72"/>
+      <c r="F20" s="141"/>
       <c r="G20" s="167"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="72"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="141"/>
       <c r="J20" s="167"/>
-      <c r="K20" s="72"/>
+      <c r="K20" s="141"/>
       <c r="L20" s="164"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="72"/>
+      <c r="M20" s="140"/>
+      <c r="N20" s="141"/>
       <c r="O20" s="164"/>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="72"/>
+      <c r="P20" s="140"/>
+      <c r="Q20" s="141"/>
       <c r="R20" s="30"/>
       <c r="S20" s="30"/>
       <c r="T20" s="31"/>
@@ -18370,22 +18488,22 @@
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
       <c r="A21" s="160"/>
-      <c r="B21" s="72"/>
+      <c r="B21" s="141"/>
       <c r="C21" s="161"/>
-      <c r="D21" s="72"/>
+      <c r="D21" s="141"/>
       <c r="E21" s="161"/>
-      <c r="F21" s="72"/>
+      <c r="F21" s="141"/>
       <c r="G21" s="167"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="72"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="141"/>
       <c r="J21" s="167"/>
-      <c r="K21" s="72"/>
+      <c r="K21" s="141"/>
       <c r="L21" s="164"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="72"/>
+      <c r="M21" s="140"/>
+      <c r="N21" s="141"/>
       <c r="O21" s="164"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="72"/>
+      <c r="P21" s="140"/>
+      <c r="Q21" s="141"/>
       <c r="R21" s="30"/>
       <c r="S21" s="30"/>
       <c r="T21" s="31"/>
@@ -18398,22 +18516,22 @@
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
       <c r="A22" s="160"/>
-      <c r="B22" s="72"/>
+      <c r="B22" s="141"/>
       <c r="C22" s="161"/>
-      <c r="D22" s="72"/>
+      <c r="D22" s="141"/>
       <c r="E22" s="161"/>
-      <c r="F22" s="72"/>
+      <c r="F22" s="141"/>
       <c r="G22" s="167"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="72"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="141"/>
       <c r="J22" s="167"/>
-      <c r="K22" s="72"/>
+      <c r="K22" s="141"/>
       <c r="L22" s="164"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="72"/>
+      <c r="M22" s="140"/>
+      <c r="N22" s="141"/>
       <c r="O22" s="164"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="72"/>
+      <c r="P22" s="140"/>
+      <c r="Q22" s="141"/>
       <c r="R22" s="30"/>
       <c r="S22" s="30"/>
       <c r="T22" s="31"/>
@@ -18426,22 +18544,22 @@
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
       <c r="A23" s="160"/>
-      <c r="B23" s="72"/>
+      <c r="B23" s="141"/>
       <c r="C23" s="161"/>
-      <c r="D23" s="72"/>
+      <c r="D23" s="141"/>
       <c r="E23" s="161"/>
-      <c r="F23" s="72"/>
+      <c r="F23" s="141"/>
       <c r="G23" s="167"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="72"/>
+      <c r="H23" s="140"/>
+      <c r="I23" s="141"/>
       <c r="J23" s="167"/>
-      <c r="K23" s="72"/>
+      <c r="K23" s="141"/>
       <c r="L23" s="164"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="72"/>
+      <c r="M23" s="140"/>
+      <c r="N23" s="141"/>
       <c r="O23" s="164"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="72"/>
+      <c r="P23" s="140"/>
+      <c r="Q23" s="141"/>
       <c r="R23" s="30"/>
       <c r="S23" s="30"/>
       <c r="T23" s="31"/>
@@ -18454,22 +18572,22 @@
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
       <c r="A24" s="160"/>
-      <c r="B24" s="72"/>
+      <c r="B24" s="141"/>
       <c r="C24" s="161"/>
-      <c r="D24" s="72"/>
+      <c r="D24" s="141"/>
       <c r="E24" s="161"/>
-      <c r="F24" s="72"/>
+      <c r="F24" s="141"/>
       <c r="G24" s="167"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="72"/>
+      <c r="H24" s="140"/>
+      <c r="I24" s="141"/>
       <c r="J24" s="167"/>
-      <c r="K24" s="72"/>
+      <c r="K24" s="141"/>
       <c r="L24" s="164"/>
-      <c r="M24" s="71"/>
-      <c r="N24" s="72"/>
+      <c r="M24" s="140"/>
+      <c r="N24" s="141"/>
       <c r="O24" s="164"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="72"/>
+      <c r="P24" s="140"/>
+      <c r="Q24" s="141"/>
       <c r="R24" s="30"/>
       <c r="S24" s="30"/>
       <c r="T24" s="31"/>
@@ -18482,22 +18600,22 @@
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
       <c r="A25" s="160"/>
-      <c r="B25" s="72"/>
+      <c r="B25" s="141"/>
       <c r="C25" s="161"/>
-      <c r="D25" s="72"/>
+      <c r="D25" s="141"/>
       <c r="E25" s="161"/>
-      <c r="F25" s="72"/>
+      <c r="F25" s="141"/>
       <c r="G25" s="167"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="72"/>
+      <c r="H25" s="140"/>
+      <c r="I25" s="141"/>
       <c r="J25" s="167"/>
-      <c r="K25" s="72"/>
+      <c r="K25" s="141"/>
       <c r="L25" s="164"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="72"/>
+      <c r="M25" s="140"/>
+      <c r="N25" s="141"/>
       <c r="O25" s="164"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="72"/>
+      <c r="P25" s="140"/>
+      <c r="Q25" s="141"/>
       <c r="R25" s="30"/>
       <c r="S25" s="30"/>
       <c r="T25" s="31"/>
@@ -18510,22 +18628,22 @@
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
       <c r="A26" s="160"/>
-      <c r="B26" s="72"/>
+      <c r="B26" s="141"/>
       <c r="C26" s="161"/>
-      <c r="D26" s="72"/>
+      <c r="D26" s="141"/>
       <c r="E26" s="161"/>
-      <c r="F26" s="72"/>
+      <c r="F26" s="141"/>
       <c r="G26" s="167"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="72"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="141"/>
       <c r="J26" s="167"/>
-      <c r="K26" s="72"/>
+      <c r="K26" s="141"/>
       <c r="L26" s="164"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="72"/>
+      <c r="M26" s="140"/>
+      <c r="N26" s="141"/>
       <c r="O26" s="164"/>
-      <c r="P26" s="71"/>
-      <c r="Q26" s="72"/>
+      <c r="P26" s="140"/>
+      <c r="Q26" s="141"/>
       <c r="R26" s="30"/>
       <c r="S26" s="30"/>
       <c r="T26" s="31"/>
@@ -18538,22 +18656,22 @@
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
       <c r="A27" s="160"/>
-      <c r="B27" s="72"/>
+      <c r="B27" s="141"/>
       <c r="C27" s="161"/>
-      <c r="D27" s="72"/>
+      <c r="D27" s="141"/>
       <c r="E27" s="161"/>
-      <c r="F27" s="72"/>
+      <c r="F27" s="141"/>
       <c r="G27" s="167"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="72"/>
+      <c r="H27" s="140"/>
+      <c r="I27" s="141"/>
       <c r="J27" s="167"/>
-      <c r="K27" s="72"/>
+      <c r="K27" s="141"/>
       <c r="L27" s="164"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="72"/>
+      <c r="M27" s="140"/>
+      <c r="N27" s="141"/>
       <c r="O27" s="164"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="72"/>
+      <c r="P27" s="140"/>
+      <c r="Q27" s="141"/>
       <c r="R27" s="30"/>
       <c r="S27" s="30"/>
       <c r="T27" s="31"/>
@@ -18566,22 +18684,22 @@
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
       <c r="A28" s="160"/>
-      <c r="B28" s="72"/>
+      <c r="B28" s="141"/>
       <c r="C28" s="161"/>
-      <c r="D28" s="72"/>
+      <c r="D28" s="141"/>
       <c r="E28" s="161"/>
-      <c r="F28" s="72"/>
+      <c r="F28" s="141"/>
       <c r="G28" s="167"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="72"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="141"/>
       <c r="J28" s="167"/>
-      <c r="K28" s="72"/>
+      <c r="K28" s="141"/>
       <c r="L28" s="164"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="72"/>
+      <c r="M28" s="140"/>
+      <c r="N28" s="141"/>
       <c r="O28" s="164"/>
-      <c r="P28" s="71"/>
-      <c r="Q28" s="72"/>
+      <c r="P28" s="140"/>
+      <c r="Q28" s="141"/>
       <c r="R28" s="30"/>
       <c r="S28" s="30"/>
       <c r="T28" s="31"/>
@@ -18594,22 +18712,22 @@
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
       <c r="A29" s="160"/>
-      <c r="B29" s="72"/>
+      <c r="B29" s="141"/>
       <c r="C29" s="161"/>
-      <c r="D29" s="72"/>
+      <c r="D29" s="141"/>
       <c r="E29" s="161"/>
-      <c r="F29" s="72"/>
+      <c r="F29" s="141"/>
       <c r="G29" s="167"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="72"/>
+      <c r="H29" s="140"/>
+      <c r="I29" s="141"/>
       <c r="J29" s="167"/>
-      <c r="K29" s="72"/>
+      <c r="K29" s="141"/>
       <c r="L29" s="164"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="72"/>
+      <c r="M29" s="140"/>
+      <c r="N29" s="141"/>
       <c r="O29" s="164"/>
-      <c r="P29" s="71"/>
-      <c r="Q29" s="72"/>
+      <c r="P29" s="140"/>
+      <c r="Q29" s="141"/>
       <c r="R29" s="30"/>
       <c r="S29" s="30"/>
       <c r="T29" s="31"/>
@@ -18622,22 +18740,22 @@
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
       <c r="A30" s="160"/>
-      <c r="B30" s="72"/>
+      <c r="B30" s="141"/>
       <c r="C30" s="161"/>
-      <c r="D30" s="72"/>
+      <c r="D30" s="141"/>
       <c r="E30" s="161"/>
-      <c r="F30" s="72"/>
+      <c r="F30" s="141"/>
       <c r="G30" s="167"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="72"/>
+      <c r="H30" s="140"/>
+      <c r="I30" s="141"/>
       <c r="J30" s="167"/>
-      <c r="K30" s="72"/>
+      <c r="K30" s="141"/>
       <c r="L30" s="164"/>
-      <c r="M30" s="71"/>
-      <c r="N30" s="72"/>
+      <c r="M30" s="140"/>
+      <c r="N30" s="141"/>
       <c r="O30" s="164"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="72"/>
+      <c r="P30" s="140"/>
+      <c r="Q30" s="141"/>
       <c r="R30" s="30"/>
       <c r="S30" s="30"/>
       <c r="T30" s="31"/>
@@ -18650,22 +18768,22 @@
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
       <c r="A31" s="162"/>
-      <c r="B31" s="77"/>
+      <c r="B31" s="157"/>
       <c r="C31" s="163"/>
-      <c r="D31" s="77"/>
+      <c r="D31" s="157"/>
       <c r="E31" s="163"/>
-      <c r="F31" s="77"/>
+      <c r="F31" s="157"/>
       <c r="G31" s="172"/>
-      <c r="H31" s="76"/>
-      <c r="I31" s="77"/>
+      <c r="H31" s="156"/>
+      <c r="I31" s="157"/>
       <c r="J31" s="172"/>
-      <c r="K31" s="77"/>
+      <c r="K31" s="157"/>
       <c r="L31" s="165"/>
-      <c r="M31" s="76"/>
-      <c r="N31" s="77"/>
+      <c r="M31" s="156"/>
+      <c r="N31" s="157"/>
       <c r="O31" s="165"/>
-      <c r="P31" s="76"/>
-      <c r="Q31" s="77"/>
+      <c r="P31" s="156"/>
+      <c r="Q31" s="157"/>
       <c r="R31" s="33"/>
       <c r="S31" s="33"/>
       <c r="T31" s="34"/>

--- a/プロジェクト型演習_成果物_TasBo_削除.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_削除.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\新しいフォルダー (2)\削除\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D749623-3011-459F-9A23-F7248BA47ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F01F307-3F4D-4A64-B0FA-1DADF5A87013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -564,13 +564,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>対象タスクが削除されている。/タスク一覧から削除対象が削除されている。</t>
-    <rPh sb="27" eb="29">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ユーザ</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -585,63 +578,71 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ユーザはタスク一覧画面で削除対象のタスクを選択する。
-システムは削除確認画面を表示する。
-ユーザは削除内容を確認する。
-ユーザは「削除確定」ボタンを押下する。
-システムは対象タスクの削除処理を実行する。
-システムは削除完了メッセージを表示する。
-システムはタスク一覧画面へ遷移する。</t>
+    <t>ユーザは自身が登録したタスクのみ削除できる。</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ユーザがシステムにログインしていること
-データベースに削除対象のタスクが存在していること
-タスク一覧画面が表示されていること
-削除対象のタスクがログイン中ユーザの登録したタスクであること</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>A1.削除をキャンセルした場合
-a. ユーザが「キャンセル」を選択する。
-b. システムは削除処理を行わない。
-c. システムは前画面（一覧または詳細画面）へ戻る。
-A2.対象タスクが既に削除されている場合
-a. システムは削除処理を開始する。
-b. 対象タスクが存在しないことを検出する。
-c. システムはエラーメッセージを表示する。
-d. システムはタスク一覧画面へ遷移する。
-A3. 他ユーザのタスクを削除しようとした場合
-a.ユーザが削除対象のタスクを選択する。
-b.システムは対象タスクの所有者を確認する。
-c.システムは対象タスクがログイン中ユーザのタスクではないことを検出する。
-d.システムは「タスクの削除は本人しか行うことはできません」などのエラーメッセージを表示する。
-e.システムはタスク一覧画面へ遷移する。</t>
-    <rPh sb="311" eb="313">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="314" eb="316">
-      <t>ホンニン</t>
-    </rPh>
-    <rPh sb="318" eb="319">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ユーザは自身が登録したタスクのみ削除できる。</t>
+    <t>・ユーザがシステムにログインしていること
+・データベースに削除対象のタスクが存在していること
+・タスク一覧画面が表示されていること</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>E1. システムエラーが発生した場合
 a. システムエラーが発生する。
-b. システムは「エラーが発生しました」等エラーメッセージを表示する。
-c. システムは処理を終了する。</t>
-    <rPh sb="49" eb="51">
-      <t>ハッセイ</t>
+b. システムは「システムエラーが発生しました。」とエラーメッセージを表示する。
+c. システムはエラー画面を表示する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>対象タスクがデータベースから削除されている。
+タスク一覧画面に対象タスクが表示されていない。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザはタスク一覧画面で削除対象のタスクを選択する。
+2.システムは対象タスクの存在を確認する。
+3.システムはログイン中ユーザが対象タスクの担当者であることを確認する。
+4.システムは削除確認画面を表示する。
+5.ユーザは削除内容を確認する。
+6.ユーザは「削除確定」ボタンを押下する。
+7.システムは再度対象タスクの存在を確認する。
+8.システムは対象タスクの削除処理を実行する。
+9.システムは削除完了画面へ遷移し、「削除に成功しました」とメッセージを表示する。</t>
+    <rPh sb="206" eb="208">
+      <t>ガメン</t>
     </rPh>
-    <rPh sb="56" eb="57">
-      <t>ナド</t>
+    <rPh sb="209" eb="211">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="214" eb="216">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="217" eb="219">
+      <t>セイコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1. 削除をキャンセルした場合（基本フロー5から分岐）
+a. ユーザが「一覧画面へ戻る」ボタンを押下する。
+b. システムは削除処理を行わない。
+c. システムはタスク一覧画面へ遷移する。
+A2. 対象タスクが既に削除されている場合(基本フロー7から分岐）
+a. システムは削除確定時に対象タスクの存在を確認する。
+b. システムは対象タスクが存在しないことを検出する。
+c. システムは「対象のタスクは既に削除されています。」とエラーメッセージを表示する。
+d. システムはタスク一覧画面へ遷移する。
+A3. 他ユーザ担当のタスクを削除しようとした場合（基本フロー3から分岐）
+a. システムは対象タスクの担当者を確認する。
+b. システムは対象タスクの担当者がログイン中ユーザではないことを検出する。
+c. システムは「タスクの削除は担当者本人のみ行えます。」とエラーメッセージを表示する。
+d. システムはタスク一覧画面へ遷移する。</t>
+    <rPh sb="90" eb="92">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="248" eb="250">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1961,39 +1962,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2168,52 +2169,52 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3714,26 +3715,26 @@
       <c r="G13" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="74"/>
+      <c r="H13" s="72"/>
       <c r="I13" s="116">
         <v>46191</v>
       </c>
       <c r="J13" s="71"/>
-      <c r="K13" s="74"/>
+      <c r="K13" s="72"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="111"/>
-      <c r="H14" s="74"/>
+      <c r="H14" s="72"/>
       <c r="I14" s="111"/>
       <c r="J14" s="71"/>
-      <c r="K14" s="74"/>
+      <c r="K14" s="72"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="111"/>
-      <c r="H15" s="74"/>
+      <c r="H15" s="72"/>
       <c r="I15" s="111"/>
       <c r="J15" s="71"/>
-      <c r="K15" s="74"/>
+      <c r="K15" s="72"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="65"/>
@@ -8375,134 +8376,134 @@
       <c r="J5" s="95"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="70" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="71"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="75" t="s">
-        <v>109</v>
+      <c r="C6" s="72"/>
+      <c r="D6" s="80" t="s">
+        <v>108</v>
       </c>
       <c r="E6" s="71"/>
       <c r="F6" s="71"/>
       <c r="G6" s="71"/>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
+      <c r="J6" s="74"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="70" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="71"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="75" t="s">
-        <v>108</v>
+      <c r="C7" s="72"/>
+      <c r="D7" s="80" t="s">
+        <v>107</v>
       </c>
       <c r="E7" s="71"/>
       <c r="F7" s="71"/>
       <c r="G7" s="71"/>
       <c r="H7" s="71"/>
       <c r="I7" s="71"/>
-      <c r="J7" s="72"/>
-    </row>
-    <row r="8" spans="1:10" ht="73.5" customHeight="1">
-      <c r="A8" s="73" t="s">
+      <c r="J7" s="74"/>
+    </row>
+    <row r="8" spans="1:10" ht="58.5" customHeight="1">
+      <c r="A8" s="70" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="71"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="70" t="s">
-        <v>111</v>
+      <c r="C8" s="72"/>
+      <c r="D8" s="73" t="s">
+        <v>110</v>
       </c>
       <c r="E8" s="71"/>
       <c r="F8" s="71"/>
       <c r="G8" s="71"/>
       <c r="H8" s="71"/>
       <c r="I8" s="71"/>
-      <c r="J8" s="72"/>
-    </row>
-    <row r="9" spans="1:10" ht="120.75" customHeight="1">
+      <c r="J8" s="74"/>
+    </row>
+    <row r="9" spans="1:10" ht="133.5" customHeight="1">
       <c r="A9" s="81" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="70" t="s">
-        <v>110</v>
+      <c r="C9" s="72"/>
+      <c r="D9" s="73" t="s">
+        <v>113</v>
       </c>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
       <c r="G9" s="71"/>
       <c r="H9" s="71"/>
       <c r="I9" s="71"/>
-      <c r="J9" s="72"/>
-    </row>
-    <row r="10" spans="1:10" ht="249.75" customHeight="1">
+      <c r="J9" s="74"/>
+    </row>
+    <row r="10" spans="1:10" ht="234" customHeight="1">
       <c r="A10" s="82"/>
       <c r="B10" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="70" t="s">
-        <v>112</v>
+      <c r="C10" s="72"/>
+      <c r="D10" s="73" t="s">
+        <v>114</v>
       </c>
       <c r="E10" s="71"/>
       <c r="F10" s="71"/>
       <c r="G10" s="71"/>
       <c r="H10" s="71"/>
       <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
+      <c r="J10" s="74"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
       <c r="A11" s="83"/>
       <c r="B11" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="70" t="s">
-        <v>114</v>
+      <c r="C11" s="72"/>
+      <c r="D11" s="73" t="s">
+        <v>111</v>
       </c>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
       <c r="H11" s="71"/>
       <c r="I11" s="71"/>
-      <c r="J11" s="72"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="73" t="s">
+      <c r="J11" s="74"/>
+    </row>
+    <row r="12" spans="1:10" ht="41.25" customHeight="1">
+      <c r="A12" s="70" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="71"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="75" t="s">
-        <v>107</v>
+      <c r="C12" s="72"/>
+      <c r="D12" s="73" t="s">
+        <v>112</v>
       </c>
       <c r="E12" s="71"/>
       <c r="F12" s="71"/>
       <c r="G12" s="71"/>
       <c r="H12" s="71"/>
       <c r="I12" s="71"/>
-      <c r="J12" s="72"/>
+      <c r="J12" s="74"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="79" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="80"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="78" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="79"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9505,6 +9506,10 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="A8:C8"/>
@@ -9516,10 +9521,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -12498,7 +12499,7 @@
         <v>54</v>
       </c>
       <c r="G2" s="135"/>
-      <c r="H2" s="153">
+      <c r="H2" s="147">
         <v>46189</v>
       </c>
       <c r="I2" s="117" t="s">
@@ -12531,23 +12532,23 @@
       <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="146" t="s">
+      <c r="D5" s="150" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="147"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="151"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="148" t="s">
+      <c r="A6" s="139" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="140"/>
@@ -12558,19 +12559,19 @@
       <c r="G6" s="140"/>
       <c r="H6" s="140"/>
       <c r="I6" s="140"/>
-      <c r="J6" s="143"/>
+      <c r="J6" s="141"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="143"/>
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="145"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="126"/>
@@ -12582,7 +12583,7 @@
       <c r="G8" s="127"/>
       <c r="H8" s="127"/>
       <c r="I8" s="127"/>
-      <c r="J8" s="152"/>
+      <c r="J8" s="146"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="126"/>
@@ -12594,7 +12595,7 @@
       <c r="G9" s="127"/>
       <c r="H9" s="127"/>
       <c r="I9" s="127"/>
-      <c r="J9" s="152"/>
+      <c r="J9" s="146"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="126"/>
@@ -12606,7 +12607,7 @@
       <c r="G10" s="127"/>
       <c r="H10" s="127"/>
       <c r="I10" s="127"/>
-      <c r="J10" s="152"/>
+      <c r="J10" s="146"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="126"/>
@@ -12618,7 +12619,7 @@
       <c r="G11" s="127"/>
       <c r="H11" s="127"/>
       <c r="I11" s="127"/>
-      <c r="J11" s="152"/>
+      <c r="J11" s="146"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="126"/>
@@ -12630,7 +12631,7 @@
       <c r="G12" s="127"/>
       <c r="H12" s="127"/>
       <c r="I12" s="127"/>
-      <c r="J12" s="152"/>
+      <c r="J12" s="146"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="126"/>
@@ -12642,10 +12643,10 @@
       <c r="G13" s="127"/>
       <c r="H13" s="127"/>
       <c r="I13" s="127"/>
-      <c r="J13" s="152"/>
+      <c r="J13" s="146"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="139" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="140"/>
@@ -12656,21 +12657,21 @@
       <c r="G14" s="140"/>
       <c r="H14" s="140"/>
       <c r="I14" s="140"/>
-      <c r="J14" s="143"/>
+      <c r="J14" s="141"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="148" t="s">
+      <c r="A15" s="139" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="140"/>
-      <c r="C15" s="141"/>
-      <c r="D15" s="142" t="s">
+      <c r="C15" s="142"/>
+      <c r="D15" s="152" t="s">
         <v>102</v>
       </c>
       <c r="E15" s="140"/>
       <c r="F15" s="140"/>
       <c r="G15" s="140"/>
-      <c r="H15" s="141"/>
+      <c r="H15" s="142"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
@@ -12679,11 +12680,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="148" t="s">
+      <c r="A16" s="139" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="140"/>
-      <c r="C16" s="141"/>
+      <c r="C16" s="142"/>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
@@ -12696,18 +12697,18 @@
       <c r="G16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="153" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="140"/>
-      <c r="J16" s="143"/>
+      <c r="J16" s="141"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="139">
+      <c r="A17" s="154">
         <v>1</v>
       </c>
       <c r="B17" s="140"/>
-      <c r="C17" s="141"/>
+      <c r="C17" s="142"/>
       <c r="D17" s="14" t="s">
         <v>101</v>
       </c>
@@ -12718,69 +12719,69 @@
       <c r="G17" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="142"/>
+      <c r="H17" s="152"/>
       <c r="I17" s="140"/>
-      <c r="J17" s="143"/>
+      <c r="J17" s="141"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="139"/>
+      <c r="A18" s="154"/>
       <c r="B18" s="140"/>
-      <c r="C18" s="141"/>
+      <c r="C18" s="142"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="142"/>
+      <c r="H18" s="152"/>
       <c r="I18" s="140"/>
-      <c r="J18" s="143"/>
+      <c r="J18" s="141"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="139"/>
+      <c r="A19" s="154"/>
       <c r="B19" s="140"/>
-      <c r="C19" s="141"/>
+      <c r="C19" s="142"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="142"/>
+      <c r="H19" s="152"/>
       <c r="I19" s="140"/>
-      <c r="J19" s="143"/>
+      <c r="J19" s="141"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="139"/>
+      <c r="A20" s="154"/>
       <c r="B20" s="140"/>
-      <c r="C20" s="141"/>
+      <c r="C20" s="142"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
-      <c r="H20" s="142"/>
+      <c r="H20" s="152"/>
       <c r="I20" s="140"/>
-      <c r="J20" s="143"/>
+      <c r="J20" s="141"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="139"/>
+      <c r="A21" s="154"/>
       <c r="B21" s="140"/>
-      <c r="C21" s="141"/>
+      <c r="C21" s="142"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="142"/>
+      <c r="H21" s="152"/>
       <c r="I21" s="140"/>
-      <c r="J21" s="143"/>
+      <c r="J21" s="141"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="139"/>
+      <c r="A22" s="154"/>
       <c r="B22" s="140"/>
-      <c r="C22" s="141"/>
+      <c r="C22" s="142"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
-      <c r="H22" s="142"/>
+      <c r="H22" s="152"/>
       <c r="I22" s="140"/>
-      <c r="J22" s="143"/>
+      <c r="J22" s="141"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A23" s="155"/>
@@ -13783,18 +13784,14 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
-    <mergeCell ref="D15:H15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -13802,8 +13799,12 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13861,7 +13862,7 @@
         <v>54</v>
       </c>
       <c r="G2" s="135"/>
-      <c r="H2" s="153">
+      <c r="H2" s="147">
         <v>46189</v>
       </c>
       <c r="I2" s="117" t="s">
@@ -13894,23 +13895,23 @@
       <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="146" t="s">
+      <c r="D5" s="150" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="147"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="151"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="148" t="s">
+      <c r="A6" s="139" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="140"/>
@@ -13921,19 +13922,19 @@
       <c r="G6" s="140"/>
       <c r="H6" s="140"/>
       <c r="I6" s="140"/>
-      <c r="J6" s="143"/>
+      <c r="J6" s="141"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="143"/>
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="145"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="126"/>
@@ -13945,7 +13946,7 @@
       <c r="G8" s="127"/>
       <c r="H8" s="127"/>
       <c r="I8" s="127"/>
-      <c r="J8" s="152"/>
+      <c r="J8" s="146"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="126"/>
@@ -13957,7 +13958,7 @@
       <c r="G9" s="127"/>
       <c r="H9" s="127"/>
       <c r="I9" s="127"/>
-      <c r="J9" s="152"/>
+      <c r="J9" s="146"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="126"/>
@@ -13969,7 +13970,7 @@
       <c r="G10" s="127"/>
       <c r="H10" s="127"/>
       <c r="I10" s="127"/>
-      <c r="J10" s="152"/>
+      <c r="J10" s="146"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="126"/>
@@ -13981,7 +13982,7 @@
       <c r="G11" s="127"/>
       <c r="H11" s="127"/>
       <c r="I11" s="127"/>
-      <c r="J11" s="152"/>
+      <c r="J11" s="146"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="126"/>
@@ -13993,7 +13994,7 @@
       <c r="G12" s="127"/>
       <c r="H12" s="127"/>
       <c r="I12" s="127"/>
-      <c r="J12" s="152"/>
+      <c r="J12" s="146"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="126"/>
@@ -14005,10 +14006,10 @@
       <c r="G13" s="127"/>
       <c r="H13" s="127"/>
       <c r="I13" s="127"/>
-      <c r="J13" s="152"/>
+      <c r="J13" s="146"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="139" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="140"/>
@@ -14019,21 +14020,21 @@
       <c r="G14" s="140"/>
       <c r="H14" s="140"/>
       <c r="I14" s="140"/>
-      <c r="J14" s="143"/>
+      <c r="J14" s="141"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="148" t="s">
+      <c r="A15" s="139" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="140"/>
-      <c r="C15" s="141"/>
-      <c r="D15" s="142" t="s">
+      <c r="C15" s="142"/>
+      <c r="D15" s="152" t="s">
         <v>96</v>
       </c>
       <c r="E15" s="140"/>
       <c r="F15" s="140"/>
       <c r="G15" s="140"/>
-      <c r="H15" s="141"/>
+      <c r="H15" s="142"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
@@ -14042,11 +14043,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="148" t="s">
+      <c r="A16" s="139" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="140"/>
-      <c r="C16" s="141"/>
+      <c r="C16" s="142"/>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
@@ -14059,18 +14060,18 @@
       <c r="G16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="153" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="140"/>
-      <c r="J16" s="143"/>
+      <c r="J16" s="141"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="139">
+      <c r="A17" s="154">
         <v>1</v>
       </c>
       <c r="B17" s="140"/>
-      <c r="C17" s="141"/>
+      <c r="C17" s="142"/>
       <c r="D17" s="14" t="s">
         <v>98</v>
       </c>
@@ -14081,24 +14082,24 @@
       <c r="G17" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="H17" s="142"/>
+      <c r="H17" s="152"/>
       <c r="I17" s="140"/>
-      <c r="J17" s="143"/>
+      <c r="J17" s="141"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="139"/>
+      <c r="A18" s="154"/>
       <c r="B18" s="140"/>
-      <c r="C18" s="141"/>
+      <c r="C18" s="142"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="142"/>
+      <c r="H18" s="152"/>
       <c r="I18" s="140"/>
-      <c r="J18" s="143"/>
+      <c r="J18" s="141"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="148" t="s">
+      <c r="A19" s="139" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="140"/>
@@ -14109,21 +14110,21 @@
       <c r="G19" s="140"/>
       <c r="H19" s="140"/>
       <c r="I19" s="140"/>
-      <c r="J19" s="143"/>
+      <c r="J19" s="141"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="148" t="s">
+      <c r="A20" s="139" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="140"/>
-      <c r="C20" s="141"/>
-      <c r="D20" s="142" t="s">
+      <c r="C20" s="142"/>
+      <c r="D20" s="152" t="s">
         <v>102</v>
       </c>
       <c r="E20" s="140"/>
       <c r="F20" s="140"/>
       <c r="G20" s="140"/>
-      <c r="H20" s="141"/>
+      <c r="H20" s="142"/>
       <c r="I20" s="12" t="s">
         <v>25</v>
       </c>
@@ -14132,11 +14133,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="148" t="s">
+      <c r="A21" s="139" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="140"/>
-      <c r="C21" s="141"/>
+      <c r="C21" s="142"/>
       <c r="D21" s="12" t="s">
         <v>27</v>
       </c>
@@ -14149,11 +14150,11 @@
       <c r="G21" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="154" t="s">
+      <c r="H21" s="153" t="s">
         <v>17</v>
       </c>
       <c r="I21" s="140"/>
-      <c r="J21" s="143"/>
+      <c r="J21" s="141"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A22" s="155">
@@ -15239,7 +15240,7 @@
         <v>54</v>
       </c>
       <c r="G2" s="135"/>
-      <c r="H2" s="153">
+      <c r="H2" s="147">
         <v>46189</v>
       </c>
       <c r="I2" s="117" t="s">
@@ -15272,23 +15273,23 @@
       <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="146" t="s">
+      <c r="D5" s="150" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="147"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="151"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="148" t="s">
+      <c r="A6" s="139" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="140"/>
@@ -15299,19 +15300,19 @@
       <c r="G6" s="140"/>
       <c r="H6" s="140"/>
       <c r="I6" s="140"/>
-      <c r="J6" s="143"/>
+      <c r="J6" s="141"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="143"/>
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="145"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="126"/>
@@ -15323,7 +15324,7 @@
       <c r="G8" s="127"/>
       <c r="H8" s="127"/>
       <c r="I8" s="127"/>
-      <c r="J8" s="152"/>
+      <c r="J8" s="146"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="126"/>
@@ -15335,7 +15336,7 @@
       <c r="G9" s="127"/>
       <c r="H9" s="127"/>
       <c r="I9" s="127"/>
-      <c r="J9" s="152"/>
+      <c r="J9" s="146"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="126"/>
@@ -15347,7 +15348,7 @@
       <c r="G10" s="127"/>
       <c r="H10" s="127"/>
       <c r="I10" s="127"/>
-      <c r="J10" s="152"/>
+      <c r="J10" s="146"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="126"/>
@@ -15359,7 +15360,7 @@
       <c r="G11" s="127"/>
       <c r="H11" s="127"/>
       <c r="I11" s="127"/>
-      <c r="J11" s="152"/>
+      <c r="J11" s="146"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="126"/>
@@ -15371,7 +15372,7 @@
       <c r="G12" s="127"/>
       <c r="H12" s="127"/>
       <c r="I12" s="127"/>
-      <c r="J12" s="152"/>
+      <c r="J12" s="146"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="126"/>
@@ -15383,10 +15384,10 @@
       <c r="G13" s="127"/>
       <c r="H13" s="127"/>
       <c r="I13" s="127"/>
-      <c r="J13" s="152"/>
+      <c r="J13" s="146"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="139" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="140"/>
@@ -15397,21 +15398,21 @@
       <c r="G14" s="140"/>
       <c r="H14" s="140"/>
       <c r="I14" s="140"/>
-      <c r="J14" s="143"/>
+      <c r="J14" s="141"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="148" t="s">
+      <c r="A15" s="139" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="140"/>
-      <c r="C15" s="141"/>
-      <c r="D15" s="142" t="s">
+      <c r="C15" s="142"/>
+      <c r="D15" s="152" t="s">
         <v>102</v>
       </c>
       <c r="E15" s="140"/>
       <c r="F15" s="140"/>
       <c r="G15" s="140"/>
-      <c r="H15" s="141"/>
+      <c r="H15" s="142"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
@@ -15420,11 +15421,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="148" t="s">
+      <c r="A16" s="139" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="140"/>
-      <c r="C16" s="141"/>
+      <c r="C16" s="142"/>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
@@ -15437,18 +15438,18 @@
       <c r="G16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="153" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="140"/>
-      <c r="J16" s="143"/>
+      <c r="J16" s="141"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="139">
+      <c r="A17" s="154">
         <v>1</v>
       </c>
       <c r="B17" s="140"/>
-      <c r="C17" s="141"/>
+      <c r="C17" s="142"/>
       <c r="D17" s="14" t="s">
         <v>101</v>
       </c>
@@ -15459,69 +15460,69 @@
       <c r="G17" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="142"/>
+      <c r="H17" s="152"/>
       <c r="I17" s="140"/>
-      <c r="J17" s="143"/>
+      <c r="J17" s="141"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="139"/>
+      <c r="A18" s="154"/>
       <c r="B18" s="140"/>
-      <c r="C18" s="141"/>
+      <c r="C18" s="142"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="142"/>
+      <c r="H18" s="152"/>
       <c r="I18" s="140"/>
-      <c r="J18" s="143"/>
+      <c r="J18" s="141"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="139"/>
+      <c r="A19" s="154"/>
       <c r="B19" s="140"/>
-      <c r="C19" s="141"/>
+      <c r="C19" s="142"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="142"/>
+      <c r="H19" s="152"/>
       <c r="I19" s="140"/>
-      <c r="J19" s="143"/>
+      <c r="J19" s="141"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="139"/>
+      <c r="A20" s="154"/>
       <c r="B20" s="140"/>
-      <c r="C20" s="141"/>
+      <c r="C20" s="142"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
-      <c r="H20" s="142"/>
+      <c r="H20" s="152"/>
       <c r="I20" s="140"/>
-      <c r="J20" s="143"/>
+      <c r="J20" s="141"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="139"/>
+      <c r="A21" s="154"/>
       <c r="B21" s="140"/>
-      <c r="C21" s="141"/>
+      <c r="C21" s="142"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="142"/>
+      <c r="H21" s="152"/>
       <c r="I21" s="140"/>
-      <c r="J21" s="143"/>
+      <c r="J21" s="141"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="139"/>
+      <c r="A22" s="154"/>
       <c r="B22" s="140"/>
-      <c r="C22" s="141"/>
+      <c r="C22" s="142"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
-      <c r="H22" s="142"/>
+      <c r="H22" s="152"/>
       <c r="I22" s="140"/>
-      <c r="J22" s="143"/>
+      <c r="J22" s="141"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A23" s="155"/>
@@ -16602,7 +16603,7 @@
         <v>54</v>
       </c>
       <c r="G2" s="135"/>
-      <c r="H2" s="153">
+      <c r="H2" s="147">
         <v>46189</v>
       </c>
       <c r="I2" s="117" t="s">
@@ -16635,23 +16636,23 @@
       <c r="J4" s="121"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="145"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="146" t="s">
+      <c r="D5" s="150" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="147"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="151"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="148" t="s">
+      <c r="A6" s="139" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="140"/>
@@ -16662,19 +16663,19 @@
       <c r="G6" s="140"/>
       <c r="H6" s="140"/>
       <c r="I6" s="140"/>
-      <c r="J6" s="143"/>
+      <c r="J6" s="141"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="149"/>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="151"/>
+      <c r="A7" s="143"/>
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="145"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="126"/>
@@ -16686,7 +16687,7 @@
       <c r="G8" s="127"/>
       <c r="H8" s="127"/>
       <c r="I8" s="127"/>
-      <c r="J8" s="152"/>
+      <c r="J8" s="146"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="126"/>
@@ -16698,7 +16699,7 @@
       <c r="G9" s="127"/>
       <c r="H9" s="127"/>
       <c r="I9" s="127"/>
-      <c r="J9" s="152"/>
+      <c r="J9" s="146"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="126"/>
@@ -16710,7 +16711,7 @@
       <c r="G10" s="127"/>
       <c r="H10" s="127"/>
       <c r="I10" s="127"/>
-      <c r="J10" s="152"/>
+      <c r="J10" s="146"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="126"/>
@@ -16722,7 +16723,7 @@
       <c r="G11" s="127"/>
       <c r="H11" s="127"/>
       <c r="I11" s="127"/>
-      <c r="J11" s="152"/>
+      <c r="J11" s="146"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="126"/>
@@ -16734,7 +16735,7 @@
       <c r="G12" s="127"/>
       <c r="H12" s="127"/>
       <c r="I12" s="127"/>
-      <c r="J12" s="152"/>
+      <c r="J12" s="146"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="126"/>
@@ -16746,10 +16747,10 @@
       <c r="G13" s="127"/>
       <c r="H13" s="127"/>
       <c r="I13" s="127"/>
-      <c r="J13" s="152"/>
+      <c r="J13" s="146"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="139" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="140"/>
@@ -16760,21 +16761,21 @@
       <c r="G14" s="140"/>
       <c r="H14" s="140"/>
       <c r="I14" s="140"/>
-      <c r="J14" s="143"/>
+      <c r="J14" s="141"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="148" t="s">
+      <c r="A15" s="139" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="140"/>
-      <c r="C15" s="141"/>
-      <c r="D15" s="142" t="s">
+      <c r="C15" s="142"/>
+      <c r="D15" s="152" t="s">
         <v>102</v>
       </c>
       <c r="E15" s="140"/>
       <c r="F15" s="140"/>
       <c r="G15" s="140"/>
-      <c r="H15" s="141"/>
+      <c r="H15" s="142"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
@@ -16783,11 +16784,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="148" t="s">
+      <c r="A16" s="139" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="140"/>
-      <c r="C16" s="141"/>
+      <c r="C16" s="142"/>
       <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
@@ -16800,18 +16801,18 @@
       <c r="G16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="153" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="140"/>
-      <c r="J16" s="143"/>
+      <c r="J16" s="141"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="139">
+      <c r="A17" s="154">
         <v>1</v>
       </c>
       <c r="B17" s="140"/>
-      <c r="C17" s="141"/>
+      <c r="C17" s="142"/>
       <c r="D17" s="14" t="s">
         <v>101</v>
       </c>
@@ -16822,69 +16823,69 @@
       <c r="G17" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="142"/>
+      <c r="H17" s="152"/>
       <c r="I17" s="140"/>
-      <c r="J17" s="143"/>
+      <c r="J17" s="141"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="139"/>
+      <c r="A18" s="154"/>
       <c r="B18" s="140"/>
-      <c r="C18" s="141"/>
+      <c r="C18" s="142"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="142"/>
+      <c r="H18" s="152"/>
       <c r="I18" s="140"/>
-      <c r="J18" s="143"/>
+      <c r="J18" s="141"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="139"/>
+      <c r="A19" s="154"/>
       <c r="B19" s="140"/>
-      <c r="C19" s="141"/>
+      <c r="C19" s="142"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="142"/>
+      <c r="H19" s="152"/>
       <c r="I19" s="140"/>
-      <c r="J19" s="143"/>
+      <c r="J19" s="141"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="139"/>
+      <c r="A20" s="154"/>
       <c r="B20" s="140"/>
-      <c r="C20" s="141"/>
+      <c r="C20" s="142"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
-      <c r="H20" s="142"/>
+      <c r="H20" s="152"/>
       <c r="I20" s="140"/>
-      <c r="J20" s="143"/>
+      <c r="J20" s="141"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="139"/>
+      <c r="A21" s="154"/>
       <c r="B21" s="140"/>
-      <c r="C21" s="141"/>
+      <c r="C21" s="142"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="142"/>
+      <c r="H21" s="152"/>
       <c r="I21" s="140"/>
-      <c r="J21" s="143"/>
+      <c r="J21" s="141"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="139"/>
+      <c r="A22" s="154"/>
       <c r="B22" s="140"/>
-      <c r="C22" s="141"/>
+      <c r="C22" s="142"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
-      <c r="H22" s="142"/>
+      <c r="H22" s="152"/>
       <c r="I22" s="140"/>
-      <c r="J22" s="143"/>
+      <c r="J22" s="141"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="155"/>
@@ -17938,14 +17939,14 @@
       <c r="G1" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
       <c r="J1" s="133"/>
       <c r="K1" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
       <c r="N1" s="133"/>
       <c r="O1" s="132" t="s">
         <v>5</v>
@@ -17958,7 +17959,7 @@
       <c r="S1" s="132" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="147"/>
+      <c r="T1" s="151"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="126"/>
@@ -17970,14 +17971,14 @@
       <c r="G2" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="150"/>
-      <c r="I2" s="150"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
       <c r="J2" s="135"/>
       <c r="K2" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="150"/>
-      <c r="M2" s="150"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
       <c r="N2" s="135"/>
       <c r="O2" s="169"/>
       <c r="P2" s="135"/>
@@ -17986,7 +17987,7 @@
       </c>
       <c r="R2" s="135"/>
       <c r="S2" s="134"/>
-      <c r="T2" s="151"/>
+      <c r="T2" s="145"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="126"/>
@@ -18008,7 +18009,7 @@
       <c r="Q3" s="136"/>
       <c r="R3" s="128"/>
       <c r="S3" s="136"/>
-      <c r="T3" s="152"/>
+      <c r="T3" s="146"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="129"/>
@@ -18033,39 +18034,39 @@
       <c r="T4" s="170"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="145"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="149"/>
+      <c r="E5" s="149"/>
       <c r="F5" s="133"/>
       <c r="G5" s="166"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="145"/>
-      <c r="K5" s="145"/>
-      <c r="L5" s="145"/>
-      <c r="M5" s="145"/>
-      <c r="N5" s="145"/>
-      <c r="O5" s="145"/>
-      <c r="P5" s="145"/>
-      <c r="Q5" s="145"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="145"/>
-      <c r="T5" s="147"/>
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="149"/>
+      <c r="K5" s="149"/>
+      <c r="L5" s="149"/>
+      <c r="M5" s="149"/>
+      <c r="N5" s="149"/>
+      <c r="O5" s="149"/>
+      <c r="P5" s="149"/>
+      <c r="Q5" s="149"/>
+      <c r="R5" s="149"/>
+      <c r="S5" s="149"/>
+      <c r="T5" s="151"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="148" t="s">
+      <c r="A6" s="139" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="140"/>
       <c r="C6" s="140"/>
       <c r="D6" s="140"/>
       <c r="E6" s="140"/>
-      <c r="F6" s="141"/>
-      <c r="G6" s="142"/>
+      <c r="F6" s="142"/>
+      <c r="G6" s="152"/>
       <c r="H6" s="140"/>
       <c r="I6" s="140"/>
       <c r="J6" s="140"/>
@@ -18078,18 +18079,18 @@
       <c r="Q6" s="140"/>
       <c r="R6" s="140"/>
       <c r="S6" s="140"/>
-      <c r="T6" s="143"/>
+      <c r="T6" s="141"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="148" t="s">
+      <c r="A7" s="139" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="140"/>
       <c r="C7" s="140"/>
       <c r="D7" s="140"/>
       <c r="E7" s="140"/>
-      <c r="F7" s="141"/>
-      <c r="G7" s="142"/>
+      <c r="F7" s="142"/>
+      <c r="G7" s="152"/>
       <c r="H7" s="140"/>
       <c r="I7" s="140"/>
       <c r="J7" s="140"/>
@@ -18102,7 +18103,7 @@
       <c r="Q7" s="140"/>
       <c r="R7" s="140"/>
       <c r="S7" s="140"/>
-      <c r="T7" s="143"/>
+      <c r="T7" s="141"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -18301,37 +18302,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="148" t="s">
+      <c r="A15" s="139" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="141"/>
+      <c r="B15" s="142"/>
       <c r="C15" s="168" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="141"/>
-      <c r="E15" s="154" t="s">
+      <c r="D15" s="142"/>
+      <c r="E15" s="153" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="141"/>
-      <c r="G15" s="154" t="s">
+      <c r="F15" s="142"/>
+      <c r="G15" s="153" t="s">
         <v>43</v>
       </c>
       <c r="H15" s="140"/>
-      <c r="I15" s="141"/>
-      <c r="J15" s="154" t="s">
+      <c r="I15" s="142"/>
+      <c r="J15" s="153" t="s">
         <v>44</v>
       </c>
-      <c r="K15" s="141"/>
-      <c r="L15" s="154" t="s">
+      <c r="K15" s="142"/>
+      <c r="L15" s="153" t="s">
         <v>45</v>
       </c>
       <c r="M15" s="140"/>
-      <c r="N15" s="141"/>
-      <c r="O15" s="154" t="s">
+      <c r="N15" s="142"/>
+      <c r="O15" s="153" t="s">
         <v>46</v>
       </c>
       <c r="P15" s="140"/>
-      <c r="Q15" s="141"/>
+      <c r="Q15" s="142"/>
       <c r="R15" s="12" t="s">
         <v>47</v>
       </c>
@@ -18346,22 +18347,22 @@
       <c r="A16" s="160">
         <v>1</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="142"/>
       <c r="C16" s="161"/>
-      <c r="D16" s="141"/>
+      <c r="D16" s="142"/>
       <c r="E16" s="161"/>
-      <c r="F16" s="141"/>
+      <c r="F16" s="142"/>
       <c r="G16" s="167"/>
       <c r="H16" s="140"/>
-      <c r="I16" s="141"/>
+      <c r="I16" s="142"/>
       <c r="J16" s="167"/>
-      <c r="K16" s="141"/>
+      <c r="K16" s="142"/>
       <c r="L16" s="164"/>
       <c r="M16" s="140"/>
-      <c r="N16" s="141"/>
+      <c r="N16" s="142"/>
       <c r="O16" s="164"/>
       <c r="P16" s="140"/>
-      <c r="Q16" s="141"/>
+      <c r="Q16" s="142"/>
       <c r="R16" s="30"/>
       <c r="S16" s="30"/>
       <c r="T16" s="31"/>
@@ -18376,22 +18377,22 @@
       <c r="A17" s="160">
         <v>2</v>
       </c>
-      <c r="B17" s="141"/>
+      <c r="B17" s="142"/>
       <c r="C17" s="161"/>
-      <c r="D17" s="141"/>
+      <c r="D17" s="142"/>
       <c r="E17" s="161"/>
-      <c r="F17" s="141"/>
+      <c r="F17" s="142"/>
       <c r="G17" s="167"/>
       <c r="H17" s="140"/>
-      <c r="I17" s="141"/>
+      <c r="I17" s="142"/>
       <c r="J17" s="167"/>
-      <c r="K17" s="141"/>
+      <c r="K17" s="142"/>
       <c r="L17" s="164"/>
       <c r="M17" s="140"/>
-      <c r="N17" s="141"/>
+      <c r="N17" s="142"/>
       <c r="O17" s="164"/>
       <c r="P17" s="140"/>
-      <c r="Q17" s="141"/>
+      <c r="Q17" s="142"/>
       <c r="R17" s="30"/>
       <c r="S17" s="30"/>
       <c r="T17" s="31"/>
@@ -18404,22 +18405,22 @@
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
       <c r="A18" s="160"/>
-      <c r="B18" s="141"/>
+      <c r="B18" s="142"/>
       <c r="C18" s="161"/>
-      <c r="D18" s="141"/>
+      <c r="D18" s="142"/>
       <c r="E18" s="161"/>
-      <c r="F18" s="141"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="167"/>
       <c r="H18" s="140"/>
-      <c r="I18" s="141"/>
+      <c r="I18" s="142"/>
       <c r="J18" s="167"/>
-      <c r="K18" s="141"/>
+      <c r="K18" s="142"/>
       <c r="L18" s="164"/>
       <c r="M18" s="140"/>
-      <c r="N18" s="141"/>
+      <c r="N18" s="142"/>
       <c r="O18" s="164"/>
       <c r="P18" s="140"/>
-      <c r="Q18" s="141"/>
+      <c r="Q18" s="142"/>
       <c r="R18" s="30"/>
       <c r="S18" s="30"/>
       <c r="T18" s="31"/>
@@ -18432,22 +18433,22 @@
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
       <c r="A19" s="160"/>
-      <c r="B19" s="141"/>
+      <c r="B19" s="142"/>
       <c r="C19" s="161"/>
-      <c r="D19" s="141"/>
+      <c r="D19" s="142"/>
       <c r="E19" s="161"/>
-      <c r="F19" s="141"/>
+      <c r="F19" s="142"/>
       <c r="G19" s="167"/>
       <c r="H19" s="140"/>
-      <c r="I19" s="141"/>
+      <c r="I19" s="142"/>
       <c r="J19" s="167"/>
-      <c r="K19" s="141"/>
+      <c r="K19" s="142"/>
       <c r="L19" s="164"/>
       <c r="M19" s="140"/>
-      <c r="N19" s="141"/>
+      <c r="N19" s="142"/>
       <c r="O19" s="164"/>
       <c r="P19" s="140"/>
-      <c r="Q19" s="141"/>
+      <c r="Q19" s="142"/>
       <c r="R19" s="30"/>
       <c r="S19" s="30"/>
       <c r="T19" s="31"/>
@@ -18460,22 +18461,22 @@
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
       <c r="A20" s="160"/>
-      <c r="B20" s="141"/>
+      <c r="B20" s="142"/>
       <c r="C20" s="161"/>
-      <c r="D20" s="141"/>
+      <c r="D20" s="142"/>
       <c r="E20" s="161"/>
-      <c r="F20" s="141"/>
+      <c r="F20" s="142"/>
       <c r="G20" s="167"/>
       <c r="H20" s="140"/>
-      <c r="I20" s="141"/>
+      <c r="I20" s="142"/>
       <c r="J20" s="167"/>
-      <c r="K20" s="141"/>
+      <c r="K20" s="142"/>
       <c r="L20" s="164"/>
       <c r="M20" s="140"/>
-      <c r="N20" s="141"/>
+      <c r="N20" s="142"/>
       <c r="O20" s="164"/>
       <c r="P20" s="140"/>
-      <c r="Q20" s="141"/>
+      <c r="Q20" s="142"/>
       <c r="R20" s="30"/>
       <c r="S20" s="30"/>
       <c r="T20" s="31"/>
@@ -18488,22 +18489,22 @@
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
       <c r="A21" s="160"/>
-      <c r="B21" s="141"/>
+      <c r="B21" s="142"/>
       <c r="C21" s="161"/>
-      <c r="D21" s="141"/>
+      <c r="D21" s="142"/>
       <c r="E21" s="161"/>
-      <c r="F21" s="141"/>
+      <c r="F21" s="142"/>
       <c r="G21" s="167"/>
       <c r="H21" s="140"/>
-      <c r="I21" s="141"/>
+      <c r="I21" s="142"/>
       <c r="J21" s="167"/>
-      <c r="K21" s="141"/>
+      <c r="K21" s="142"/>
       <c r="L21" s="164"/>
       <c r="M21" s="140"/>
-      <c r="N21" s="141"/>
+      <c r="N21" s="142"/>
       <c r="O21" s="164"/>
       <c r="P21" s="140"/>
-      <c r="Q21" s="141"/>
+      <c r="Q21" s="142"/>
       <c r="R21" s="30"/>
       <c r="S21" s="30"/>
       <c r="T21" s="31"/>
@@ -18516,22 +18517,22 @@
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
       <c r="A22" s="160"/>
-      <c r="B22" s="141"/>
+      <c r="B22" s="142"/>
       <c r="C22" s="161"/>
-      <c r="D22" s="141"/>
+      <c r="D22" s="142"/>
       <c r="E22" s="161"/>
-      <c r="F22" s="141"/>
+      <c r="F22" s="142"/>
       <c r="G22" s="167"/>
       <c r="H22" s="140"/>
-      <c r="I22" s="141"/>
+      <c r="I22" s="142"/>
       <c r="J22" s="167"/>
-      <c r="K22" s="141"/>
+      <c r="K22" s="142"/>
       <c r="L22" s="164"/>
       <c r="M22" s="140"/>
-      <c r="N22" s="141"/>
+      <c r="N22" s="142"/>
       <c r="O22" s="164"/>
       <c r="P22" s="140"/>
-      <c r="Q22" s="141"/>
+      <c r="Q22" s="142"/>
       <c r="R22" s="30"/>
       <c r="S22" s="30"/>
       <c r="T22" s="31"/>
@@ -18544,22 +18545,22 @@
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
       <c r="A23" s="160"/>
-      <c r="B23" s="141"/>
+      <c r="B23" s="142"/>
       <c r="C23" s="161"/>
-      <c r="D23" s="141"/>
+      <c r="D23" s="142"/>
       <c r="E23" s="161"/>
-      <c r="F23" s="141"/>
+      <c r="F23" s="142"/>
       <c r="G23" s="167"/>
       <c r="H23" s="140"/>
-      <c r="I23" s="141"/>
+      <c r="I23" s="142"/>
       <c r="J23" s="167"/>
-      <c r="K23" s="141"/>
+      <c r="K23" s="142"/>
       <c r="L23" s="164"/>
       <c r="M23" s="140"/>
-      <c r="N23" s="141"/>
+      <c r="N23" s="142"/>
       <c r="O23" s="164"/>
       <c r="P23" s="140"/>
-      <c r="Q23" s="141"/>
+      <c r="Q23" s="142"/>
       <c r="R23" s="30"/>
       <c r="S23" s="30"/>
       <c r="T23" s="31"/>
@@ -18572,22 +18573,22 @@
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
       <c r="A24" s="160"/>
-      <c r="B24" s="141"/>
+      <c r="B24" s="142"/>
       <c r="C24" s="161"/>
-      <c r="D24" s="141"/>
+      <c r="D24" s="142"/>
       <c r="E24" s="161"/>
-      <c r="F24" s="141"/>
+      <c r="F24" s="142"/>
       <c r="G24" s="167"/>
       <c r="H24" s="140"/>
-      <c r="I24" s="141"/>
+      <c r="I24" s="142"/>
       <c r="J24" s="167"/>
-      <c r="K24" s="141"/>
+      <c r="K24" s="142"/>
       <c r="L24" s="164"/>
       <c r="M24" s="140"/>
-      <c r="N24" s="141"/>
+      <c r="N24" s="142"/>
       <c r="O24" s="164"/>
       <c r="P24" s="140"/>
-      <c r="Q24" s="141"/>
+      <c r="Q24" s="142"/>
       <c r="R24" s="30"/>
       <c r="S24" s="30"/>
       <c r="T24" s="31"/>
@@ -18600,22 +18601,22 @@
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
       <c r="A25" s="160"/>
-      <c r="B25" s="141"/>
+      <c r="B25" s="142"/>
       <c r="C25" s="161"/>
-      <c r="D25" s="141"/>
+      <c r="D25" s="142"/>
       <c r="E25" s="161"/>
-      <c r="F25" s="141"/>
+      <c r="F25" s="142"/>
       <c r="G25" s="167"/>
       <c r="H25" s="140"/>
-      <c r="I25" s="141"/>
+      <c r="I25" s="142"/>
       <c r="J25" s="167"/>
-      <c r="K25" s="141"/>
+      <c r="K25" s="142"/>
       <c r="L25" s="164"/>
       <c r="M25" s="140"/>
-      <c r="N25" s="141"/>
+      <c r="N25" s="142"/>
       <c r="O25" s="164"/>
       <c r="P25" s="140"/>
-      <c r="Q25" s="141"/>
+      <c r="Q25" s="142"/>
       <c r="R25" s="30"/>
       <c r="S25" s="30"/>
       <c r="T25" s="31"/>
@@ -18628,22 +18629,22 @@
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
       <c r="A26" s="160"/>
-      <c r="B26" s="141"/>
+      <c r="B26" s="142"/>
       <c r="C26" s="161"/>
-      <c r="D26" s="141"/>
+      <c r="D26" s="142"/>
       <c r="E26" s="161"/>
-      <c r="F26" s="141"/>
+      <c r="F26" s="142"/>
       <c r="G26" s="167"/>
       <c r="H26" s="140"/>
-      <c r="I26" s="141"/>
+      <c r="I26" s="142"/>
       <c r="J26" s="167"/>
-      <c r="K26" s="141"/>
+      <c r="K26" s="142"/>
       <c r="L26" s="164"/>
       <c r="M26" s="140"/>
-      <c r="N26" s="141"/>
+      <c r="N26" s="142"/>
       <c r="O26" s="164"/>
       <c r="P26" s="140"/>
-      <c r="Q26" s="141"/>
+      <c r="Q26" s="142"/>
       <c r="R26" s="30"/>
       <c r="S26" s="30"/>
       <c r="T26" s="31"/>
@@ -18656,22 +18657,22 @@
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
       <c r="A27" s="160"/>
-      <c r="B27" s="141"/>
+      <c r="B27" s="142"/>
       <c r="C27" s="161"/>
-      <c r="D27" s="141"/>
+      <c r="D27" s="142"/>
       <c r="E27" s="161"/>
-      <c r="F27" s="141"/>
+      <c r="F27" s="142"/>
       <c r="G27" s="167"/>
       <c r="H27" s="140"/>
-      <c r="I27" s="141"/>
+      <c r="I27" s="142"/>
       <c r="J27" s="167"/>
-      <c r="K27" s="141"/>
+      <c r="K27" s="142"/>
       <c r="L27" s="164"/>
       <c r="M27" s="140"/>
-      <c r="N27" s="141"/>
+      <c r="N27" s="142"/>
       <c r="O27" s="164"/>
       <c r="P27" s="140"/>
-      <c r="Q27" s="141"/>
+      <c r="Q27" s="142"/>
       <c r="R27" s="30"/>
       <c r="S27" s="30"/>
       <c r="T27" s="31"/>
@@ -18684,22 +18685,22 @@
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
       <c r="A28" s="160"/>
-      <c r="B28" s="141"/>
+      <c r="B28" s="142"/>
       <c r="C28" s="161"/>
-      <c r="D28" s="141"/>
+      <c r="D28" s="142"/>
       <c r="E28" s="161"/>
-      <c r="F28" s="141"/>
+      <c r="F28" s="142"/>
       <c r="G28" s="167"/>
       <c r="H28" s="140"/>
-      <c r="I28" s="141"/>
+      <c r="I28" s="142"/>
       <c r="J28" s="167"/>
-      <c r="K28" s="141"/>
+      <c r="K28" s="142"/>
       <c r="L28" s="164"/>
       <c r="M28" s="140"/>
-      <c r="N28" s="141"/>
+      <c r="N28" s="142"/>
       <c r="O28" s="164"/>
       <c r="P28" s="140"/>
-      <c r="Q28" s="141"/>
+      <c r="Q28" s="142"/>
       <c r="R28" s="30"/>
       <c r="S28" s="30"/>
       <c r="T28" s="31"/>
@@ -18712,22 +18713,22 @@
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
       <c r="A29" s="160"/>
-      <c r="B29" s="141"/>
+      <c r="B29" s="142"/>
       <c r="C29" s="161"/>
-      <c r="D29" s="141"/>
+      <c r="D29" s="142"/>
       <c r="E29" s="161"/>
-      <c r="F29" s="141"/>
+      <c r="F29" s="142"/>
       <c r="G29" s="167"/>
       <c r="H29" s="140"/>
-      <c r="I29" s="141"/>
+      <c r="I29" s="142"/>
       <c r="J29" s="167"/>
-      <c r="K29" s="141"/>
+      <c r="K29" s="142"/>
       <c r="L29" s="164"/>
       <c r="M29" s="140"/>
-      <c r="N29" s="141"/>
+      <c r="N29" s="142"/>
       <c r="O29" s="164"/>
       <c r="P29" s="140"/>
-      <c r="Q29" s="141"/>
+      <c r="Q29" s="142"/>
       <c r="R29" s="30"/>
       <c r="S29" s="30"/>
       <c r="T29" s="31"/>
@@ -18740,22 +18741,22 @@
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
       <c r="A30" s="160"/>
-      <c r="B30" s="141"/>
+      <c r="B30" s="142"/>
       <c r="C30" s="161"/>
-      <c r="D30" s="141"/>
+      <c r="D30" s="142"/>
       <c r="E30" s="161"/>
-      <c r="F30" s="141"/>
+      <c r="F30" s="142"/>
       <c r="G30" s="167"/>
       <c r="H30" s="140"/>
-      <c r="I30" s="141"/>
+      <c r="I30" s="142"/>
       <c r="J30" s="167"/>
-      <c r="K30" s="141"/>
+      <c r="K30" s="142"/>
       <c r="L30" s="164"/>
       <c r="M30" s="140"/>
-      <c r="N30" s="141"/>
+      <c r="N30" s="142"/>
       <c r="O30" s="164"/>
       <c r="P30" s="140"/>
-      <c r="Q30" s="141"/>
+      <c r="Q30" s="142"/>
       <c r="R30" s="30"/>
       <c r="S30" s="30"/>
       <c r="T30" s="31"/>
